--- a/INSTANCES/instances_xlsx/A_MTN_8/334FL_15A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/334FL_15A_4.xlsx
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -10790,7 +10790,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -10807,7 +10807,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -10858,7 +10858,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -10875,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -10943,7 +10943,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
